--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>8.47</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>86.50</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>40.70</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.70</t>
+          <t>41.47</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.67</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1455.02</t>
+          <t>1440.11</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>96.79</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>36.98</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>9.30</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>86.50</t>
+          <t>80.02</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>40.70</t>
+          <t>37.63</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>40.68</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>39.18</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1440.11</t>
+          <t>1426.19</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.79</t>
+          <t>95.21</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.98</t>
+          <t>33.28</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>8.37</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>79.40</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>36.87</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>38.79</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.18</t>
+          <t>38.60</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1426.19</t>
+          <t>1401.18</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>95.99</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>34.69</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.42</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>81.13</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>35.93</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>36.87</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.60</t>
+          <t>39.15</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1401.18</t>
+          <t>1399.04</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>94.47</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>35.03</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>8.28</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>80.18</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>34.87</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.00</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.20</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1399.04</t>
+          <t>1402.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.47</t>
+          <t>93.62</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>35.15</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.90</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.18</t>
+          <t>81.79</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>34.38</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>36.99</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.20</t>
+          <t>38.79</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1402.00</t>
+          <t>1397.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.62</t>
+          <t>97.52</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>34.41</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>7.94</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.79</t>
+          <t>82.73</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>34.74</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>36.49</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>39.22</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1401.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>97.52</t>
+          <t>96.60</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>35.18</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>8.26</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.73</t>
+          <t>82.82</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34.74</t>
+          <t>33.88</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>35.48</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>39.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1401.88</t>
+          <t>1400.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.60</t>
+          <t>99.22</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>35.82</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.19</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.82</t>
+          <t>81.61</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.04</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>34.58</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1392.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.22</t>
+          <t>99.10</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>34.26</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.32</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.61</t>
+          <t>79.18</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>31.87</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>32.98</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.50</t>
+          <t>39.76</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1413.64</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.10</t>
+          <t>99.67</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>32.32</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.49</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>80.38</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.06</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>31.71</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.91</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1413.64</t>
+          <t>1460.18</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.67</t>
+          <t>104.62</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>31.59</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>8.26</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.38</t>
+          <t>77.17</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>30.80</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.55</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>40.12</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1460.18</t>
+          <t>1485.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>102.87</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>30.30</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.38</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.17</t>
+          <t>79.89</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.80</t>
+          <t>30.70</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.49</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>39.92</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1485.00</t>
+          <t>1468.80</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102.87</t>
+          <t>101.69</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>31.52</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>8.02</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.89</t>
+          <t>77.63</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.70</t>
+          <t>28.68</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>29.60</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>39.77</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1468.80</t>
+          <t>1452.87</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.69</t>
+          <t>102.31</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>31.86</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>7.99</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.63</t>
+          <t>76.46</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>28.00</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>29.40</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.75</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1452.87</t>
+          <t>1445.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102.31</t>
+          <t>103.03</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>30.50</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.91</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>70.33</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>26.30</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>27.30</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>38.68</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1408.07</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>107.63</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>29.83</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.20</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>70.33</t>
+          <t>72.00</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.30</t>
+          <t>26.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.30</t>
+          <t>28.29</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>39.25</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1408.07</t>
+          <t>1407.33</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>107.63</t>
+          <t>106.64</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>30.42</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>8.39</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>73.78</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>27.93</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.93</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.26</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1407.33</t>
+          <t>1410.27</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>106.64</t>
+          <t>106.60</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>30.20</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>8.79</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>71.21</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>27.09</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>28.13</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.56</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1410.27</t>
+          <t>1401.18</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>106.60</t>
+          <t>103.14</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>29.62</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>8.97</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>71.21</t>
+          <t>70.45</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>28.11</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>29.25</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>39.44</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1401.18</t>
+          <t>1416.02</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>105.30</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.16</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>69.92</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>28.50</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>30.40</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>39.48</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1416.02</t>
+          <t>1420.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>105.30</t>
+          <t>106.05</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>32.58</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>8.99</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>69.20</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.50</t>
+          <t>28.19</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>30.90</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>39.32</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1420.00</t>
+          <t>1450.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>105.25</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>34.38</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>9.15</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>69.20</t>
+          <t>70.18</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.19</t>
+          <t>28.69</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.90</t>
+          <t>31.03</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.82</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1459.44</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>105.25</t>
+          <t>102.65</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>33.21</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.60</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>67.12</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>27.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>29.33</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>39.76</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1459.44</t>
+          <t>1459.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102.65</t>
+          <t>101.65</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>32.36</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.42</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>66.79</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>29.05</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>39.40</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1459.88</t>
+          <t>1460.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.65</t>
+          <t>99.01</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>31.41</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>9.20</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>66.79</t>
+          <t>67.51</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.15</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.40</t>
+          <t>38.99</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1460.00</t>
+          <t>1440.02</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.01</t>
+          <t>97.98</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>31.43</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>9.41</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>67.51</t>
+          <t>71.60</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>32.07</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>39.62</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1440.02</t>
+          <t>1465.02</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>97.98</t>
+          <t>101.22</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>33.03</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.48</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>71.60</t>
+          <t>71.35</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>31.03</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>39.26</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1465.02</t>
+          <t>1460.49</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.22</t>
+          <t>99.03</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>32.58</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>9.15</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>71.35</t>
+          <t>75.00</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>30.48</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>39.21</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1460.49</t>
+          <t>1453.96</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.03</t>
+          <t>101.67</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>32.00</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>8.88</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>77.21</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>29.70</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>29.60</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>38.98</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1453.96</t>
+          <t>1443.31</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.67</t>
+          <t>104.25</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>31.81</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>8.76</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>78.19</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.70</t>
+          <t>29.31</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>29.52</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>39.13</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1443.31</t>
+          <t>1446.90</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>104.25</t>
+          <t>103.82</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>33.97</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>9.03</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>78.19</t>
+          <t>76.50</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>28.84</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>29.18</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>39.90</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1446.90</t>
+          <t>1467.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103.82</t>
+          <t>103.03</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>34.93</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>9.11</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.50</t>
+          <t>79.70</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>29.30</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>29.74</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.90</t>
+          <t>39.91</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1467.50</t>
+          <t>1462.84</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>105.54</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>35.28</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.70</t>
+          <t>82.20</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.30</t>
+          <t>31.49</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>30.15</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.52</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1462.84</t>
+          <t>1407.24</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>105.54</t>
+          <t>103.78</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>35.67</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.95</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.20</t>
+          <t>87.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>31.53</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.39</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>39.87</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1407.24</t>
+          <t>1410.89</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>103.78</t>
+          <t>102.91</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>37.39</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.99</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>87.80</t>
+          <t>82.04</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>32.78</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>30.88</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1410.89</t>
+          <t>1412.01</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>101.53</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.62</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>9.15</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.04</t>
+          <t>86.12</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>33.89</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>31.35</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>39.74</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1412.01</t>
+          <t>1409.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.53</t>
+          <t>101.62</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>38.40</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>9.06</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>86.12</t>
+          <t>81.88</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>32.56</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>29.89</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.74</t>
+          <t>39.81</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1409.50</t>
+          <t>1419.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.62</t>
+          <t>99.98</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>38.40</t>
+          <t>36.38</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>78.45</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>32.70</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.51</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>39.38</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1419.00</t>
+          <t>1458.49</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.98</t>
+          <t>99.46</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>35.01</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.92</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>77.71</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.70</t>
+          <t>31.82</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>28.85</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1458.49</t>
+          <t>1403.20</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.46</t>
+          <t>102.34</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>34.22</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>9.03</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.71</t>
+          <t>75.95</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>30.38</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>27.98</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>39.60</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1403.20</t>
+          <t>1405.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102.34</t>
+          <t>101.48</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>32.84</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>8.58</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>76.83</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>29.37</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>28.99</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.60</t>
+          <t>38.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1401.17</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.48</t>
+          <t>105.40</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>33.26</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>8.56</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.83</t>
+          <t>78.73</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>28.66</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>29.07</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>38.27</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1401.17</t>
+          <t>1384.79</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>105.40</t>
+          <t>102.98</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.52</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>8.54</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>78.73</t>
+          <t>82.48</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>30.31</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>30.26</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.00</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1384.79</t>
+          <t>1375.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>102.98</t>
+          <t>100.75</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>34.78</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.48</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.48</t>
+          <t>85.05</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.31</t>
+          <t>29.93</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>30.40</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>37.95</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1371.05</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100.75</t>
+          <t>100.46</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>34.98</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>85.15</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.93</t>
+          <t>30.35</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>30.51</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.94</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1371.05</t>
+          <t>1372.99</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100.46</t>
+          <t>100.02</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>38.48</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.25</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>84.97</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.20</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>29.83</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.97</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1372.99</t>
+          <t>1361.33</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.19</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.16</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>84.97</t>
+          <t>83.89</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30.20</t>
+          <t>29.55</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.24</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>37.90</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1361.33</t>
+          <t>1354.55</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>99.23</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>38.19</t>
+          <t>38.50</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>8.22</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>87.49</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.25</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>28.95</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.90</t>
+          <t>37.88</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1354.55</t>
+          <t>1344.09</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>99.23</t>
+          <t>98.60</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>40.12</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>8.33</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>83.85</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>27.97</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>27.75</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.88</t>
+          <t>37.81</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1344.09</t>
+          <t>1342.17</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>98.60</t>
+          <t>98.73</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>36.71</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>83.85</t>
+          <t>81.90</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>27.36</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>26.32</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.65</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1342.17</t>
+          <t>1332.95</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>98.73</t>
+          <t>96.30</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>35.27</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.73</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.90</t>
+          <t>83.06</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>28.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>26.02</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.47</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1332.95</t>
+          <t>1323.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.30</t>
+          <t>94.51</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>35.40</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>7.75</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>84.45</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.21</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>25.69</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>37.37</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1323.00</t>
+          <t>1324.30</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.51</t>
+          <t>96.00</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.40</t>
+          <t>34.67</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.96</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>84.45</t>
+          <t>85.91</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>27.53</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.51</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.17</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1324.30</t>
+          <t>1315.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>93.36</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>33.63</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.87</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.91</t>
+          <t>81.00</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>26.57</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>24.69</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.17</t>
+          <t>37.15</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1311.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.36</t>
+          <t>93.51</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>32.50</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>83.56</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.90</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>25.19</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>37.02</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1311.00</t>
+          <t>1290.20</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.51</t>
+          <t>93.75</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>32.43</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>7.75</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>83.56</t>
+          <t>85.08</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.90</t>
+          <t>26.76</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>25.47</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>36.94</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1290.20</t>
+          <t>1285.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>95.96</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>32.84</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.54</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>79.54</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>25.03</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>24.64</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>37.12</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1285.88</t>
+          <t>1275.98</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95.96</t>
+          <t>95.88</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>28.15</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>7.80</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>76.70</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>24.56</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.28</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>38.01</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1275.98</t>
+          <t>1326.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>96.18</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>26.15</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>74.51</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>24.84</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>24.39</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.20</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1326.00</t>
+          <t>1309.60</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.18</t>
+          <t>93.65</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.72</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.05</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>74.51</t>
+          <t>74.95</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>25.09</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>25.64</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.20</t>
+          <t>38.80</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1309.60</t>
+          <t>1307.22</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>96.76</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.33</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.76</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>74.95</t>
+          <t>75.42</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>25.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.48</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.80</t>
+          <t>38.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1307.22</t>
+          <t>1281.91</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.76</t>
+          <t>94.82</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.80</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>7.61</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>73.40</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>24.94</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>24.87</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>38.10</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1281.91</t>
+          <t>1268.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.82</t>
+          <t>93.44</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.80</t>
+          <t>25.02</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.92</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>73.40</t>
+          <t>76.29</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>24.10</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>24.45</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.10</t>
+          <t>38.58</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1272.86</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.44</t>
+          <t>93.01</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.86</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>7.48</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.29</t>
+          <t>74.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.10</t>
+          <t>22.19</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>23.03</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>38.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1272.86</t>
+          <t>1262.98</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.01</t>
+          <t>91.19</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>26.20</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.70</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>74.80</t>
+          <t>78.28</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.19</t>
+          <t>21.83</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>23.70</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>38.49</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1262.98</t>
+          <t>1256.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.19</t>
+          <t>91.89</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>26.20</t>
+          <t>25.19</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.70</t>
+          <t>7.66</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>78.22</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>20.77</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.70</t>
+          <t>22.98</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>38.90</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1256.00</t>
+          <t>1275.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.89</t>
+          <t>90.31</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>24.37</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.83</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>78.22</t>
+          <t>74.97</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>20.54</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.98</t>
+          <t>23.33</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.90</t>
+          <t>38.73</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1275.88</t>
+          <t>1279.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>89.80</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>23.60</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>7.99</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>74.97</t>
+          <t>74.07</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>21.58</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>24.23</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>39.34</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1279.00</t>
+          <t>1291.91</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.80</t>
+          <t>91.60</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.60</t>
+          <t>25.08</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>8.19</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>77.02</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>23.03</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>25.65</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>38.95</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1291.91</t>
+          <t>1271.10</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.60</t>
+          <t>90.82</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>24.29</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>7.93</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.02</t>
+          <t>74.87</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>25.33</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>26.60</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.57</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1271.10</t>
+          <t>1255.67</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>89.64</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.42</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.96</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>75.39</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>24.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>26.50</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>38.23</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1255.67</t>
+          <t>1240.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.64</t>
+          <t>87.47</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.50</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>7.86</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75.39</t>
+          <t>76.82</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.43</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.50</t>
+          <t>26.66</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>37.26</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1240.00</t>
+          <t>1215.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>88.13</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>24.88</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>8.15</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.82</t>
+          <t>75.59</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.87</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>29.15</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.65</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1215.00</t>
+          <t>1241.41</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>87.59</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>24.39</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.36</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75.59</t>
+          <t>80.90</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>24.49</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>26.24</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.40</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1241.41</t>
+          <t>1222.45</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>85.00</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.39</t>
+          <t>23.61</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>8.16</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.90</t>
+          <t>82.96</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>25.20</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>26.06</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.40</t>
+          <t>36.76</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1222.45</t>
+          <t>1207.68</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>83.30</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>24.61</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>8.18</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.96</t>
+          <t>86.96</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25.20</t>
+          <t>24.75</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>25.65</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>36.23</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1207.68</t>
+          <t>1212.10</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.30</t>
+          <t>82.20</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>23.88</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.09</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>85.40</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>23.60</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>24.24</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.23</t>
+          <t>36.00</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1212.10</t>
+          <t>1168.63</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.20</t>
+          <t>78.20</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>26.27</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8.25</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.40</t>
+          <t>81.49</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.60</t>
+          <t>24.15</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.35</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>36.42</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1168.63</t>
+          <t>1194.96</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>78.20</t>
+          <t>79.64</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>27.13</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>7.81</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.49</t>
+          <t>85.70</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.99</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>23.87</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>35.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1194.96</t>
+          <t>1185.49</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>79.64</t>
+          <t>79.70</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>27.13</t>
+          <t>28.02</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>8.23</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.70</t>
+          <t>82.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>23.87</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.87</t>
+          <t>23.80</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>35.50</t>
+          <t>35.91</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1185.49</t>
+          <t>1193.01</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>79.70</t>
+          <t>80.66</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>29.46</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.53</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>82.80</t>
+          <t>79.40</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.87</t>
+          <t>23.77</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.80</t>
+          <t>24.56</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>36.60</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1193.01</t>
+          <t>1203.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>83.57</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>28.00</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.63</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>80.58</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>25.93</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.60</t>
+          <t>36.83</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1203.00</t>
+          <t>1194.45</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.57</t>
+          <t>88.47</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>28.02</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>8.64</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>81.08</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>22.74</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>24.22</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>37.73</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1194.45</t>
+          <t>1206.91</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>87.54</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>25.95</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.29</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81.08</t>
+          <t>76.30</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>21.57</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>23.06</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.73</t>
+          <t>37.55</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1206.91</t>
+          <t>1188.80</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>86.26</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>24.95</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.20</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>77.83</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>21.02</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>22.91</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.94</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1188.80</t>
+          <t>1199.30</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>87.80</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>23.66</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>8.17</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.83</t>
+          <t>79.60</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>20.92</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>24.26</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>37.55</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1199.30</t>
+          <t>1182.19</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.80</t>
+          <t>86.87</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>25.20</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.99</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.60</t>
+          <t>80.72</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>20.80</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.76</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>36.88</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1182.19</t>
+          <t>1204.98</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.87</t>
+          <t>90.00</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.20</t>
+          <t>27.72</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>9.82</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80.72</t>
+          <t>79.19</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.80</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>22.20</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>37.25</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1204.98</t>
+          <t>1210.99</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>86.98</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>24.95</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.58</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79.19</t>
+          <t>83.52</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.38</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>22.72</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.18</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1210.99</t>
+          <t>1214.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.98</t>
+          <t>90.18</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>22.46</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>10.57</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>83.52</t>
+          <t>78.70</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>18.82</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>22.21</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>37.76</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1214.88</t>
+          <t>1251.06</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>91.76</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>20.21</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>10.40</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>78.70</t>
+          <t>76.24</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>19.23</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>21.96</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>37.67</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1251.06</t>
+          <t>1258.99</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>94.14</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.25</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.40</t>
+          <t>10.56</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76.24</t>
+          <t>68.98</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>17.97</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>20.76</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>38.02</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1258.99</t>
+          <t>1253.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.14</t>
+          <t>93.47</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>17.75</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>11.17</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>68.98</t>
+          <t>68.03</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>17.53</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>20.83</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>38.91</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1253.00</t>
+          <t>1327.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.47</t>
+          <t>93.92</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.32</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>10.90</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>70.00</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>22.23</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>37.99</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1327.50</t>
+          <t>1308.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>94.30</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.40</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.90</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>71.16</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>18.48</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>23.01</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>38.71</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1308.00</t>
+          <t>1305.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.30</t>
+          <t>91.57</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>16.98</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>68.32</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>23.34</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>38.91</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1305.00</t>
+          <t>1292.01</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.57</t>
+          <t>92.65</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>18.68</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>10.69</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>68.32</t>
+          <t>64.60</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>17.77</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>22.18</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>39.20</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1292.01</t>
+          <t>1297.41</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92.65</t>
+          <t>91.89</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>17.20</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>10.80</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>65.20</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>18.64</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.78</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.20</t>
+          <t>39.00</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1297.41</t>
+          <t>1289.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.89</t>
+          <t>92.40</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.20</t>
+          <t>18.15</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>11.20</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>65.20</t>
+          <t>62.47</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.25</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>22.31</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>39.59</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1289.50</t>
+          <t>1320.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92.40</t>
+          <t>93.35</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.49</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>11.24</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.47</t>
+          <t>61.15</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.71</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>22.81</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>39.66</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1320.00</t>
+          <t>1321.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.35</t>
+          <t>94.85</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>17.70</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>10.98</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>54.68</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.88</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>22.44</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>40.55</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1321.00</t>
+          <t>1361.76</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.85</t>
+          <t>96.20</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.70</t>
+          <t>16.83</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.31</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>54.68</t>
+          <t>56.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>19.52</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.05</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>39.62</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1361.76</t>
+          <t>1350.60</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>96.20</t>
+          <t>95.77</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>17.48</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>11.35</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56.80</t>
+          <t>56.97</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.83</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.81</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>40.36</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1350.60</t>
+          <t>1358.98</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95.77</t>
+          <t>94.45</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>18.06</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.58</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>59.30</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>20.19</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.81</t>
+          <t>23.04</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>39.28</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1358.98</t>
+          <t>1328.36</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.45</t>
+          <t>91.15</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>18.64</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>11.73</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.30</t>
+          <t>60.80</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.94</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>24.68</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.94</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1328.36</t>
+          <t>1306.45</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.15</t>
+          <t>90.82</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>19.01</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>60.80</t>
+          <t>61.02</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>20.70</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>25.15</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>38.97</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1306.45</t>
+          <t>1308.55</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>89.45</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.56</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>11.95</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>62.53</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>21.15</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>25.78</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>38.80</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1308.55</t>
+          <t>1309.22</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>90.04</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>20.28</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>11.65</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.53</t>
+          <t>60.87</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>23.27</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>27.08</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.80</t>
+          <t>38.91</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1309.22</t>
+          <t>1348.86</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>91.15</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>20.70</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>11.43</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>60.90</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>22.66</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>25.70</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>38.95</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1348.86</t>
+          <t>1346.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.15</t>
+          <t>90.12</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>19.58</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>12.06</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>60.90</t>
+          <t>61.14</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>22.80</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.70</t>
+          <t>25.87</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.70</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1346.50</t>
+          <t>1343.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>90.41</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>11.85</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>61.14</t>
+          <t>61.77</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>21.91</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>24.73</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.70</t>
+          <t>38.77</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1343.00</t>
+          <t>1355.29</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.71</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.66</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.81</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>61.77</t>
+          <t>62.26</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>21.94</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>24.65</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>38.46</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1355.29</t>
+          <t>1341.99</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>88.90</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.86</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>11.82</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>64.00</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>22.09</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.10</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.20</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1341.99</t>
+          <t>1293.09</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.90</t>
+          <t>89.88</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>20.57</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>12.09</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>64.00</t>
+          <t>63.23</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.70</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t>25.02</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.20</t>
+          <t>38.29</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1293.09</t>
+          <t>1297.99</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.53</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>20.42</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>11.92</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>59.38</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.70</t>
+          <t>20.85</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>24.56</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.29</t>
+          <t>39.15</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1297.99</t>
+          <t>1307.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.66</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>18.59</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.48</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>59.29</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>21.27</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.86</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1307.88</t>
+          <t>1291.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>90.48</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>18.04</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.48</t>
+          <t>11.83</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>59.94</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>22.14</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>38.90</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1291.50</t>
+          <t>1272.83</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.47</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>18.31</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>11.35</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>62.29</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>23.29</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.90</t>
+          <t>39.58</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1272.83</t>
+          <t>1304.66</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.66</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.80</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>11.26</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>62.29</t>
+          <t>65.77</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>21.80</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.50</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1304.66</t>
+          <t>1304.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.66</t>
+          <t>91.36</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>18.18</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>11.15</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>65.77</t>
+          <t>58.59</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21.80</t>
+          <t>22.29</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.50</t>
+          <t>39.80</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1302.80</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>92.09</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>18.06</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>10.98</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>57.96</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.63</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>27.02</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.80</t>
+          <t>39.58</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1302.80</t>
+          <t>1292.30</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>91.49</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>18.34</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>11.47</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>56.73</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>23.80</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>28.92</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.35</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1292.30</t>
+          <t>1297.40</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>92.32</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.24</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>11.49</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>59.08</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.80</t>
+          <t>23.20</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>27.23</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>40.12</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1297.40</t>
+          <t>1299.52</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>88.20</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>18.36</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>11.67</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59.08</t>
+          <t>58.16</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.20</t>
+          <t>22.65</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>26.45</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>40.86</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1299.52</t>
+          <t>1299.56</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.20</t>
+          <t>88.71</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.25</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.17</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>61.60</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.26</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.21</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40.87</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1299.56</t>
+          <t>1297.50</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>86.80</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.26</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>11.65</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>61.60</t>
+          <t>63.62</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>23.38</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.21</t>
+          <t>27.54</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>41.07</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1297.50</t>
+          <t>1298.88</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86.80</t>
+          <t>87.31</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>18.20</t>
         </is>
       </c>
     </row>

--- a/src/files/workflow_files/now_price8.xlsx
+++ b/src/files/workflow_files/now_price8.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>11.66</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>63.38</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>22.61</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>26.78</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>41.07</t>
+          <t>41.69</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1298.88</t>
+          <t>1330.00</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>87.40</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18.20</t>
+          <t>18.24</t>
         </is>
       </c>
     </row>
